--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-016_祝日管理_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-016_祝日管理_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="8810625"/>
+    <ext cx="8572500" cy="9020175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-016 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-016 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="49" customHeight="1">
+    <row r="3" ht="109" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -1862,7 +1862,9 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：未定義だった private notFound()（E-015 / 404）と toResponse の定義を追加、updated_at をトリガ自動更新に変更、共通基盤への追加改修の参照先を ONL-001 に統一</t>
+          <t>・確定設計変更 D1〜D10 を反映：未定義だった private notFound()（E-015 / 404）と toResponse の定義を追加、updated_at をトリガ自動更新に変更、共通基盤への追加改修の参照先を ONL-001 に統一
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）
+・HolidayService に Clock を注入（年の既定値を本日の年にするため）</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -3053,7 +3055,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>2000〜2099。未指定は本日(JST)の年</t>
+          <t>2000〜2099。未指定は本日(clock)の年</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -4106,7 +4108,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>対象年。null は今年(JST)</t>
+          <t>対象年。null は今年(clock)</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
